--- a/00 Raw data/General_Metrics .xlsx
+++ b/00 Raw data/General_Metrics .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\線上追蹤平台\研究量能追蹤平台\nkust-research-platform\00 Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A475313A-5CB9-4CBB-973C-6F9E56610C7C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86B58B9-66D4-426C-A347-1EC6010EDDB0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,8 +243,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -562,4664 +563,4666 @@
   <dimension ref="A1:P108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" customWidth="1"/>
-    <col min="4" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="27.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="23.21875" style="1" customWidth="1"/>
+    <col min="4" max="6" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="1">
         <v>2017</v>
       </c>
-      <c r="H1">
+      <c r="H1" s="1">
         <v>2018</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="1">
         <v>2019</v>
       </c>
-      <c r="J1">
+      <c r="J1" s="1">
         <v>2020</v>
       </c>
-      <c r="K1">
+      <c r="K1" s="1">
         <v>2021</v>
       </c>
-      <c r="L1">
+      <c r="L1" s="1">
         <v>2022</v>
       </c>
-      <c r="M1">
+      <c r="M1" s="1">
         <v>2023</v>
       </c>
-      <c r="N1">
+      <c r="N1" s="1">
         <v>2024</v>
       </c>
-      <c r="O1">
+      <c r="O1" s="1">
         <v>2025</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1">
         <v>232</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>270</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>244</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>252</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>251</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>288</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>301</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>298</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>370</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>2506</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
         <v>817</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>692</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>752</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>853</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>979</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>1175</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>1086</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>1141</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>1310</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>8805</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1">
         <v>267</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>268</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>347</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>351</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>453</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>522</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>483</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>505</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>544</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>3740</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1">
         <v>1164</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>1222</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>1233</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>1382</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>1464</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>1593</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>1474</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>1543</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>1752</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>12827</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1">
         <v>1416</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>1329</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>1470</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>1585</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>1716</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>1687</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>1748</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>1713</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>1948</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>14612</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1">
         <v>434</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>474</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>554</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>692</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>942</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>1022</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>930</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>876</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>1016</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>6940</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1">
         <v>38386</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>37971</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>39282</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>42196</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>46554</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>48206</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>45267</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>46126</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>49813</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>393801</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
+      <c r="E10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1">
         <v>24</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>27</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>28</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>27</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>28</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>28</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>26</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>28</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>29</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
+      <c r="E11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="1">
         <v>36</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>34</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>32</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>35</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>41</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>50</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>60</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>75</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>88</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
+      <c r="E12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1">
         <v>26</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>24</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>27</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>31</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>35</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>38</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>40</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>42</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>46</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
+      <c r="E13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1">
         <v>46</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>50</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>55</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>61</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>64</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>68</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>73</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>74</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>77</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
+      <c r="E14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1">
         <v>57</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>64</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>69</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>67</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>72</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>82</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>87</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>93</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>96</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
+      <c r="E15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1">
         <v>28</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>28</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>29</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>30</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>38</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>56</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>74</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>93</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>103</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="P16" t="s">
+      <c r="P16" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18">
+      <c r="E18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1">
         <v>0.72</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>0.61</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>0.48</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>0.62</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0.8</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>0.65</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>0.65</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>0.56999999999999995</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>0.62</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
+      <c r="E19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1">
         <v>0.71</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>0.74</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>0.83</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>0.92</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>1.06</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>1.1299999999999999</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>1.07</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>1.03</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>0.92</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>0.95</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20">
+      <c r="E20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1">
         <v>0.76</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>0.79</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>0.95</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>0.93</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0.84</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>1.01</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>0.91</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>0.83</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>0.97</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>0.9</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21">
+      <c r="E21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1">
         <v>0.91</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>0.91</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>1.06</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>1.04</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>1</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>1.01</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>1.06</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>1.07</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>1.45</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>1.07</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22">
+      <c r="E22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1">
         <v>1.1100000000000001</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>1.1499999999999999</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>1.1599999999999999</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>1.24</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>1.23</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>1.21</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>1.2</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>1.1399999999999999</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>1.24</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>1.19</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23">
+      <c r="E23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1">
         <v>0.65</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>0.69</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="1">
         <v>0.84</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="1">
         <v>1.28</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>1.84</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="1">
         <v>2.25</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="1">
         <v>1.94</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="1">
         <v>4.01</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="1">
         <v>2.34</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="1">
         <v>1.97</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24">
+      <c r="E24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1">
         <v>1.03</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>1.0900000000000001</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>1.1200000000000001</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>1.2</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>1.2</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="1">
         <v>1.22</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="1">
         <v>1.27</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="1">
         <v>1.25</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="1">
         <v>1.18</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26">
+      <c r="D26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="1">
         <v>15.1</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>12.2</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="1">
         <v>16.399999999999999</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>21</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>17.100000000000001</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>18.100000000000001</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="1">
         <v>15.9</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="1">
         <v>18.8</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="1">
         <v>23.2</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="1">
         <v>17.8</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27">
+      <c r="D27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="1">
         <v>20.3</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>24.7</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="1">
         <v>26.7</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
         <v>33.6</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>34.1</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>37.799999999999997</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="1">
         <v>38.9</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="1">
         <v>37.700000000000003</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="1">
         <v>41.3</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="1">
         <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28">
+      <c r="D28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="1">
         <v>22.1</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>28.4</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="1">
         <v>31.7</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>32.799999999999997</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>36.9</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>37.700000000000003</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="1">
         <v>36.6</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="1">
         <v>38.200000000000003</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="1">
         <v>38.6</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="1">
         <v>34.9</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D29" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29">
+      <c r="D29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1">
         <v>23.8</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>31.8</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="1">
         <v>34.5</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>36</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>39.1</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>42.1</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="1">
         <v>41</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="1">
         <v>43.1</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="1">
         <v>42.1</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="1">
         <v>37.700000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D30" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30">
+      <c r="D30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1">
         <v>28.9</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>33.200000000000003</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="1">
         <v>36.1</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1">
         <v>39.4</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>39.200000000000003</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>38.4</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="1">
         <v>40.299999999999997</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="1">
         <v>40.799999999999997</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="1">
         <v>41.1</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="1">
         <v>37.799999999999997</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D31" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31">
+      <c r="D31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="1">
         <v>18.2</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>22.4</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="1">
         <v>28.9</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="1">
         <v>46.1</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>55.4</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="1">
         <v>62.7</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="1">
         <v>57.3</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="1">
         <v>55.6</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="1">
         <v>55.3</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="1">
         <v>49.1</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D32" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32">
+      <c r="D32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1">
         <v>32.1</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>34.799999999999997</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="1">
         <v>37</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
         <v>40.9</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>41.5</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="1">
         <v>42.1</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="1">
         <v>42.1</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="1">
         <v>43.2</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="1">
         <v>43.9</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="1">
         <v>40.1</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D34" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34">
+      <c r="D34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="1">
         <v>35</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>33</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="1">
         <v>40</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="1">
         <v>53</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>43</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="1">
         <v>52</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="1">
         <v>48</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="1">
         <v>56</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="1">
         <v>86</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="1">
         <v>446</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D35" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35">
+      <c r="D35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="1">
         <v>166</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
         <v>171</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="1">
         <v>201</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="1">
         <v>287</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="1">
         <v>334</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="1">
         <v>444</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="1">
         <v>422</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="1">
         <v>430</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="1">
         <v>541</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="1">
         <v>2996</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D36" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36">
+      <c r="D36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1">
         <v>59</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="1">
         <v>76</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="1">
         <v>110</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="1">
         <v>115</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="1">
         <v>167</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="1">
         <v>197</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="1">
         <v>177</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="1">
         <v>193</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="1">
         <v>210</v>
       </c>
-      <c r="P36">
+      <c r="P36" s="1">
         <v>1304</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37">
+      <c r="D37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="1">
         <v>277</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
         <v>388</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="1">
         <v>426</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="1">
         <v>498</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="1">
         <v>572</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="1">
         <v>671</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="1">
         <v>605</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="1">
         <v>665</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="1">
         <v>737</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="1">
         <v>4839</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D38" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38">
+      <c r="D38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="1">
         <v>409</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <v>441</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="1">
         <v>530</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="1">
         <v>625</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="1">
         <v>673</v>
       </c>
-      <c r="L38">
+      <c r="L38" s="1">
         <v>648</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="1">
         <v>704</v>
       </c>
-      <c r="N38">
+      <c r="N38" s="1">
         <v>699</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="1">
         <v>800</v>
       </c>
-      <c r="P38">
+      <c r="P38" s="1">
         <v>5529</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39">
+      <c r="D39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1">
         <v>79</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <v>106</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="1">
         <v>160</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="1">
         <v>319</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="1">
         <v>522</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="1">
         <v>641</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="1">
         <v>533</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="1">
         <v>487</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="1">
         <v>562</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="1">
         <v>3409</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40">
+      <c r="D40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="1">
         <v>12309</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
         <v>13195</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="1">
         <v>14515</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="1">
         <v>17260</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="1">
         <v>19319</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="1">
         <v>20272</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="1">
         <v>19068</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="1">
         <v>19920</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="1">
         <v>21864</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="1">
         <v>157722</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42">
+      <c r="D42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="1">
         <v>37.700000000000003</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="1">
         <v>10.6</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="1">
         <v>11.6</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="1">
         <v>18.7</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="1">
         <v>30.6</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="1">
         <v>12.4</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="1">
         <v>9.4</v>
       </c>
-      <c r="N42">
+      <c r="N42" s="1">
         <v>4.2</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="1">
         <v>2.5</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="1">
         <v>13.4</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D43" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43">
+      <c r="D43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="1">
         <v>16.7</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
         <v>25.8</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="1">
         <v>24</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="1">
         <v>30.8</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="1">
         <v>32.799999999999997</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="1">
         <v>33.200000000000003</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="1">
         <v>23.7</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="1">
         <v>12.8</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="1">
         <v>21.5</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44">
+      <c r="D44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="1">
         <v>27.3</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="1">
         <v>23.3</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="1">
         <v>28.3</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="1">
         <v>24.1</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="1">
         <v>19.7</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="1">
         <v>18.7</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="1">
         <v>12.5</v>
       </c>
-      <c r="N44">
+      <c r="N44" s="1">
         <v>9.5</v>
       </c>
-      <c r="O44">
+      <c r="O44" s="1">
         <v>3.5</v>
       </c>
-      <c r="P44">
+      <c r="P44" s="1">
         <v>16.100000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45">
+      <c r="D45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="1">
         <v>46.2</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="1">
         <v>34.1</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="1">
         <v>38.1</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="1">
         <v>33.4</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="1">
         <v>27.6</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="1">
         <v>22.2</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="1">
         <v>18.7</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="1">
         <v>14.8</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="1">
         <v>6.8</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="1">
         <v>23.9</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D46" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46">
+      <c r="D46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="1">
         <v>37</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="1">
         <v>40</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="1">
         <v>36.9</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="1">
         <v>41.5</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="1">
         <v>31.6</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="1">
         <v>25</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="1">
         <v>19.7</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="1">
         <v>13.4</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="1">
         <v>6.2</v>
       </c>
-      <c r="P46">
+      <c r="P46" s="1">
         <v>26.1</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47">
+      <c r="D47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="1">
         <v>26.8</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="1">
         <v>27.6</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="1">
         <v>30.2</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="1">
         <v>43.3</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="1">
         <v>53.2</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="1">
         <v>43</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="1">
         <v>34</v>
       </c>
-      <c r="N47">
+      <c r="N47" s="1">
         <v>39.9</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="1">
         <v>10.5</v>
       </c>
-      <c r="P47">
+      <c r="P47" s="1">
         <v>35.9</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48">
+      <c r="D48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="1">
         <v>43.9</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="1">
         <v>41.9</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="1">
         <v>39.299999999999997</v>
       </c>
-      <c r="J48">
+      <c r="J48" s="1">
         <v>40.9</v>
       </c>
-      <c r="K48">
+      <c r="K48" s="1">
         <v>31.8</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="1">
         <v>25.8</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="1">
         <v>19.5</v>
       </c>
-      <c r="N48">
+      <c r="N48" s="1">
         <v>13.7</v>
       </c>
-      <c r="O48">
+      <c r="O48" s="1">
         <v>5.5</v>
       </c>
-      <c r="P48">
+      <c r="P48" s="1">
         <v>27.1</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50">
+      <c r="D50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="1">
         <v>0.4</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="1">
         <v>0</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="1">
         <v>0.8</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="1">
         <v>0.4</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="1">
         <v>1.6</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="1">
         <v>1.4</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="1">
         <v>3.7</v>
       </c>
-      <c r="N50">
+      <c r="N50" s="1">
         <v>3.4</v>
       </c>
-      <c r="O50">
+      <c r="O50" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="P50">
+      <c r="P50" s="1">
         <v>1.6</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51">
+      <c r="D51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="1">
         <v>1.4</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="1">
         <v>1.6</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="1">
         <v>1.4</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="1">
         <v>1.9</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="1">
         <v>2</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="1">
         <v>2.4</v>
       </c>
-      <c r="N51">
+      <c r="N51" s="1">
         <v>1.8</v>
       </c>
-      <c r="O51">
+      <c r="O51" s="1">
         <v>3.1</v>
       </c>
-      <c r="P51">
+      <c r="P51" s="1">
         <v>2.1</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52">
+      <c r="D52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="1">
         <v>1.9</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="1">
         <v>0.3</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="1">
         <v>0</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="1">
         <v>0.9</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="1">
         <v>1</v>
       </c>
-      <c r="M52">
+      <c r="M52" s="1">
         <v>0.4</v>
       </c>
-      <c r="N52">
+      <c r="N52" s="1">
         <v>0.6</v>
       </c>
-      <c r="O52">
+      <c r="O52" s="1">
         <v>2.8</v>
       </c>
-      <c r="P52">
+      <c r="P52" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" t="s">
-        <v>10</v>
-      </c>
-      <c r="G53">
+      <c r="D53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="1">
         <v>2.1</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="1">
         <v>2.9</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="1">
         <v>2.9</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="1">
         <v>3</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="1">
         <v>2.9</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="M53">
+      <c r="M53" s="1">
         <v>2.5</v>
       </c>
-      <c r="N53">
+      <c r="N53" s="1">
         <v>2.7</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="1">
         <v>2.5</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="1">
         <v>2.9</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D54" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54">
+      <c r="D54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="1">
         <v>2.8</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="1">
         <v>2.1</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="1">
         <v>1.8</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="1">
         <v>2</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="1">
         <v>2.5</v>
       </c>
-      <c r="L54">
+      <c r="L54" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="M54">
+      <c r="M54" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="N54">
+      <c r="N54" s="1">
         <v>2.5</v>
       </c>
-      <c r="O54">
+      <c r="O54" s="1">
         <v>3.2</v>
       </c>
-      <c r="P54">
+      <c r="P54" s="1">
         <v>2.4</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="s">
-        <v>10</v>
-      </c>
-      <c r="G55">
+      <c r="D55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="1">
         <v>3.7</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="1">
         <v>3.2</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J55">
+      <c r="J55" s="1">
         <v>1</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="1">
         <v>1.9</v>
       </c>
-      <c r="L55">
+      <c r="L55" s="1">
         <v>3.2</v>
       </c>
-      <c r="M55">
+      <c r="M55" s="1">
         <v>1.6</v>
       </c>
-      <c r="N55">
+      <c r="N55" s="1">
         <v>1.7</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="1">
         <v>1.5</v>
       </c>
-      <c r="P55">
+      <c r="P55" s="1">
         <v>2.1</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D56" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56">
+      <c r="D56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="1">
         <v>3.1</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="1">
         <v>3</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="1">
         <v>2.8</v>
       </c>
-      <c r="J56">
+      <c r="J56" s="1">
         <v>2.7</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="1">
         <v>2.9</v>
       </c>
-      <c r="L56">
+      <c r="L56" s="1">
         <v>3.1</v>
       </c>
-      <c r="M56">
+      <c r="M56" s="1">
         <v>3.3</v>
       </c>
-      <c r="N56">
+      <c r="N56" s="1">
         <v>3.5</v>
       </c>
-      <c r="O56">
+      <c r="O56" s="1">
         <v>3.5</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="1">
         <v>3.1</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D58" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58">
+      <c r="D58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="1">
         <v>1</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="1">
         <v>0</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="1">
         <v>2</v>
       </c>
-      <c r="J58">
+      <c r="J58" s="1">
         <v>1</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="1">
         <v>4</v>
       </c>
-      <c r="L58">
+      <c r="L58" s="1">
         <v>4</v>
       </c>
-      <c r="M58">
-        <v>11</v>
-      </c>
-      <c r="N58">
-        <v>10</v>
-      </c>
-      <c r="O58">
+      <c r="M58" s="1">
+        <v>11</v>
+      </c>
+      <c r="N58" s="1">
+        <v>10</v>
+      </c>
+      <c r="O58" s="1">
         <v>8</v>
       </c>
-      <c r="P58">
+      <c r="P58" s="1">
         <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="A59" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D59" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" t="s">
-        <v>10</v>
-      </c>
-      <c r="G59">
+      <c r="D59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="1">
         <v>18</v>
       </c>
-      <c r="H59">
-        <v>10</v>
-      </c>
-      <c r="I59">
+      <c r="H59" s="1">
+        <v>10</v>
+      </c>
+      <c r="I59" s="1">
         <v>12</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="1">
         <v>12</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="1">
         <v>19</v>
       </c>
-      <c r="L59">
+      <c r="L59" s="1">
         <v>23</v>
       </c>
-      <c r="M59">
+      <c r="M59" s="1">
         <v>26</v>
       </c>
-      <c r="N59">
+      <c r="N59" s="1">
         <v>20</v>
       </c>
-      <c r="O59">
+      <c r="O59" s="1">
         <v>41</v>
       </c>
-      <c r="P59">
+      <c r="P59" s="1">
         <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="A60" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D60" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60">
+      <c r="D60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="1">
         <v>3</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="1">
         <v>5</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="1">
         <v>1</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="1">
         <v>0</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="1">
         <v>4</v>
       </c>
-      <c r="L60">
+      <c r="L60" s="1">
         <v>5</v>
       </c>
-      <c r="M60">
+      <c r="M60" s="1">
         <v>2</v>
       </c>
-      <c r="N60">
+      <c r="N60" s="1">
         <v>3</v>
       </c>
-      <c r="O60">
+      <c r="O60" s="1">
         <v>15</v>
       </c>
-      <c r="P60">
+      <c r="P60" s="1">
         <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="A61" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61">
+      <c r="D61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="1">
         <v>24</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="1">
         <v>35</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="1">
         <v>36</v>
       </c>
-      <c r="J61">
+      <c r="J61" s="1">
         <v>41</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="1">
         <v>42</v>
       </c>
-      <c r="L61">
+      <c r="L61" s="1">
         <v>74</v>
       </c>
-      <c r="M61">
+      <c r="M61" s="1">
         <v>37</v>
       </c>
-      <c r="N61">
+      <c r="N61" s="1">
         <v>41</v>
       </c>
-      <c r="O61">
+      <c r="O61" s="1">
         <v>43</v>
       </c>
-      <c r="P61">
+      <c r="P61" s="1">
         <v>373</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="A62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D62" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62">
+      <c r="D62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="1">
         <v>39</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="1">
         <v>28</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="1">
         <v>27</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="1">
         <v>31</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="1">
         <v>43</v>
       </c>
-      <c r="L62">
+      <c r="L62" s="1">
         <v>39</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="1">
         <v>41</v>
       </c>
-      <c r="N62">
+      <c r="N62" s="1">
         <v>42</v>
       </c>
-      <c r="O62">
+      <c r="O62" s="1">
         <v>63</v>
       </c>
-      <c r="P62">
+      <c r="P62" s="1">
         <v>353</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="A63" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D63" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63">
+      <c r="D63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="1">
         <v>16</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="1">
         <v>15</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="1">
         <v>12</v>
       </c>
-      <c r="J63">
+      <c r="J63" s="1">
         <v>7</v>
       </c>
-      <c r="K63">
+      <c r="K63" s="1">
         <v>18</v>
       </c>
-      <c r="L63">
+      <c r="L63" s="1">
         <v>33</v>
       </c>
-      <c r="M63">
+      <c r="M63" s="1">
         <v>15</v>
       </c>
-      <c r="N63">
+      <c r="N63" s="1">
         <v>15</v>
       </c>
-      <c r="O63">
+      <c r="O63" s="1">
         <v>15</v>
       </c>
-      <c r="P63">
+      <c r="P63" s="1">
         <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="A64" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D64" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" t="s">
-        <v>10</v>
-      </c>
-      <c r="G64">
+      <c r="D64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" s="1">
         <v>1178</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="1">
         <v>1131</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="1">
         <v>1084</v>
       </c>
-      <c r="J64">
+      <c r="J64" s="1">
         <v>1138</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="1">
         <v>1359</v>
       </c>
-      <c r="L64">
+      <c r="L64" s="1">
         <v>1518</v>
       </c>
-      <c r="M64">
+      <c r="M64" s="1">
         <v>1488</v>
       </c>
-      <c r="N64">
+      <c r="N64" s="1">
         <v>1619</v>
       </c>
-      <c r="O64">
+      <c r="O64" s="1">
         <v>1753</v>
       </c>
-      <c r="P64">
+      <c r="P64" s="1">
         <v>12268</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="A65" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="A66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D66" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66">
-        <v>10</v>
-      </c>
-      <c r="H66" t="s">
-        <v>10</v>
-      </c>
-      <c r="I66">
+      <c r="D66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="1">
+        <v>10</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I66" s="1">
         <v>1</v>
       </c>
-      <c r="J66">
+      <c r="J66" s="1">
         <v>2</v>
       </c>
-      <c r="K66">
+      <c r="K66" s="1">
         <v>98.3</v>
       </c>
-      <c r="L66">
+      <c r="L66" s="1">
         <v>15</v>
       </c>
-      <c r="M66">
+      <c r="M66" s="1">
         <v>6.7</v>
       </c>
-      <c r="N66">
+      <c r="N66" s="1">
         <v>8.5</v>
       </c>
-      <c r="O66">
+      <c r="O66" s="1">
         <v>2.6</v>
       </c>
-      <c r="P66">
+      <c r="P66" s="1">
         <v>15.8</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="A67" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D67" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67">
+      <c r="D67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="1">
         <v>9.8000000000000007</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="1">
         <v>11.8</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="1">
         <v>9.8000000000000007</v>
       </c>
-      <c r="J67">
+      <c r="J67" s="1">
         <v>31.9</v>
       </c>
-      <c r="K67">
+      <c r="K67" s="1">
         <v>19.8</v>
       </c>
-      <c r="L67">
+      <c r="L67" s="1">
         <v>17.399999999999999</v>
       </c>
-      <c r="M67">
+      <c r="M67" s="1">
         <v>10.5</v>
       </c>
-      <c r="N67">
+      <c r="N67" s="1">
         <v>18.8</v>
       </c>
-      <c r="O67">
+      <c r="O67" s="1">
         <v>3.2</v>
       </c>
-      <c r="P67">
+      <c r="P67" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="A68" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D68" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68">
+      <c r="D68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="1">
         <v>18.3</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="1">
         <v>8</v>
       </c>
-      <c r="I68" t="s">
-        <v>10</v>
-      </c>
-      <c r="J68" t="s">
-        <v>10</v>
-      </c>
-      <c r="K68">
+      <c r="I68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K68" s="1">
         <v>7</v>
       </c>
-      <c r="L68">
+      <c r="L68" s="1">
         <v>13.4</v>
       </c>
-      <c r="M68">
+      <c r="M68" s="1">
         <v>13</v>
       </c>
-      <c r="N68">
+      <c r="N68" s="1">
         <v>1.3</v>
       </c>
-      <c r="O68">
+      <c r="O68" s="1">
         <v>3.6</v>
       </c>
-      <c r="P68">
+      <c r="P68" s="1">
         <v>7.2</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="A69" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D69" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69">
+      <c r="D69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="1">
         <v>24.2</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="1">
         <v>28.1</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="1">
         <v>12.2</v>
       </c>
-      <c r="J69">
+      <c r="J69" s="1">
         <v>22.5</v>
       </c>
-      <c r="K69">
+      <c r="K69" s="1">
         <v>15.5</v>
       </c>
-      <c r="L69">
+      <c r="L69" s="1">
         <v>14</v>
       </c>
-      <c r="M69">
+      <c r="M69" s="1">
         <v>15.8</v>
       </c>
-      <c r="N69">
+      <c r="N69" s="1">
         <v>11.9</v>
       </c>
-      <c r="O69">
+      <c r="O69" s="1">
         <v>4.2</v>
       </c>
-      <c r="P69">
+      <c r="P69" s="1">
         <v>15.7</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="A70" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D70" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" t="s">
-        <v>10</v>
-      </c>
-      <c r="G70">
+      <c r="D70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="1">
         <v>18.600000000000001</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="1">
         <v>35.299999999999997</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="1">
         <v>26.8</v>
       </c>
-      <c r="J70">
+      <c r="J70" s="1">
         <v>31.7</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="1">
         <v>25.8</v>
       </c>
-      <c r="L70">
+      <c r="L70" s="1">
         <v>24</v>
       </c>
-      <c r="M70">
+      <c r="M70" s="1">
         <v>15.1</v>
       </c>
-      <c r="N70">
+      <c r="N70" s="1">
         <v>11.9</v>
       </c>
-      <c r="O70">
+      <c r="O70" s="1">
         <v>4</v>
       </c>
-      <c r="P70">
+      <c r="P70" s="1">
         <v>19.399999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="A71" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D71" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" t="s">
-        <v>10</v>
-      </c>
-      <c r="G71">
+      <c r="D71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" s="1">
         <v>7.3</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="1">
         <v>6.9</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="1">
         <v>13.6</v>
       </c>
-      <c r="J71">
+      <c r="J71" s="1">
         <v>36.1</v>
       </c>
-      <c r="K71">
+      <c r="K71" s="1">
         <v>62.7</v>
       </c>
-      <c r="L71">
+      <c r="L71" s="1">
         <v>143.1</v>
       </c>
-      <c r="M71">
+      <c r="M71" s="1">
         <v>167.8</v>
       </c>
-      <c r="N71">
+      <c r="N71" s="1">
         <v>685.1</v>
       </c>
-      <c r="O71">
+      <c r="O71" s="1">
         <v>115.4</v>
       </c>
-      <c r="P71">
+      <c r="P71" s="1">
         <v>143.9</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="A72" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D72" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72">
+      <c r="D72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="1">
         <v>92.8</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="1">
         <v>99.6</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="1">
         <v>69</v>
       </c>
-      <c r="J72">
+      <c r="J72" s="1">
         <v>98.8</v>
       </c>
-      <c r="K72">
+      <c r="K72" s="1">
         <v>52.6</v>
       </c>
-      <c r="L72">
+      <c r="L72" s="1">
         <v>47.5</v>
       </c>
-      <c r="M72">
+      <c r="M72" s="1">
         <v>30.8</v>
       </c>
-      <c r="N72">
+      <c r="N72" s="1">
         <v>32</v>
       </c>
-      <c r="O72">
+      <c r="O72" s="1">
         <v>9.5</v>
       </c>
-      <c r="P72">
+      <c r="P72" s="1">
         <v>54.4</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="A74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E74" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="E74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="1">
         <v>6</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="1">
         <v>5.6</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J74">
+      <c r="J74" s="1">
         <v>5.6</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="1">
         <v>4</v>
       </c>
-      <c r="L74">
+      <c r="L74" s="1">
         <v>6.6</v>
       </c>
-      <c r="M74">
+      <c r="M74" s="1">
         <v>4</v>
       </c>
-      <c r="N74">
+      <c r="N74" s="1">
         <v>5.4</v>
       </c>
-      <c r="O74">
+      <c r="O74" s="1">
         <v>7.8</v>
       </c>
-      <c r="P74">
+      <c r="P74" s="1">
         <v>5.5</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E75" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="E75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="1">
         <v>6.9</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="1">
         <v>8.1</v>
       </c>
-      <c r="J75">
+      <c r="J75" s="1">
         <v>13.4</v>
       </c>
-      <c r="K75">
+      <c r="K75" s="1">
         <v>15.7</v>
       </c>
-      <c r="L75">
+      <c r="L75" s="1">
         <v>17.5</v>
       </c>
-      <c r="M75">
+      <c r="M75" s="1">
         <v>18.3</v>
       </c>
-      <c r="N75">
+      <c r="N75" s="1">
         <v>14.7</v>
       </c>
-      <c r="O75">
+      <c r="O75" s="1">
         <v>16.3</v>
       </c>
-      <c r="P75">
+      <c r="P75" s="1">
         <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E76" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="E76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="1">
         <v>9.4</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="1">
         <v>11.6</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="1">
         <v>12.4</v>
       </c>
-      <c r="J76">
+      <c r="J76" s="1">
         <v>10.8</v>
       </c>
-      <c r="K76">
+      <c r="K76" s="1">
         <v>11.5</v>
       </c>
-      <c r="L76">
+      <c r="L76" s="1">
         <v>11.5</v>
       </c>
-      <c r="M76">
+      <c r="M76" s="1">
         <v>9.1</v>
       </c>
-      <c r="N76">
+      <c r="N76" s="1">
         <v>8.3000000000000007</v>
       </c>
-      <c r="O76">
+      <c r="O76" s="1">
         <v>11.2</v>
       </c>
-      <c r="P76">
+      <c r="P76" s="1">
         <v>10.6</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="A77" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E77" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="E77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="1">
         <v>12.3</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="1">
         <v>11.9</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="1">
         <v>14.6</v>
       </c>
-      <c r="J77">
+      <c r="J77" s="1">
         <v>15.3</v>
       </c>
-      <c r="K77">
+      <c r="K77" s="1">
         <v>15.2</v>
       </c>
-      <c r="L77">
+      <c r="L77" s="1">
         <v>15.8</v>
       </c>
-      <c r="M77">
+      <c r="M77" s="1">
         <v>18.7</v>
       </c>
-      <c r="N77">
+      <c r="N77" s="1">
         <v>19.600000000000001</v>
       </c>
-      <c r="O77">
+      <c r="O77" s="1">
         <v>23</v>
       </c>
-      <c r="P77">
+      <c r="P77" s="1">
         <v>16.600000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E78" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="E78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="1">
         <v>11.4</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="1">
         <v>13.9</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="1">
         <v>16.3</v>
       </c>
-      <c r="J78">
+      <c r="J78" s="1">
         <v>17.2</v>
       </c>
-      <c r="K78">
+      <c r="K78" s="1">
         <v>19.2</v>
       </c>
-      <c r="L78">
+      <c r="L78" s="1">
         <v>19</v>
       </c>
-      <c r="M78">
+      <c r="M78" s="1">
         <v>20.2</v>
       </c>
-      <c r="N78">
+      <c r="N78" s="1">
         <v>20.8</v>
       </c>
-      <c r="O78">
+      <c r="O78" s="1">
         <v>20.2</v>
       </c>
-      <c r="P78">
+      <c r="P78" s="1">
         <v>17.899999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="A79" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E79" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="E79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="1">
         <v>5.3</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="1">
         <v>9.1</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="1">
         <v>10.5</v>
       </c>
-      <c r="J79">
+      <c r="J79" s="1">
         <v>16.600000000000001</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="1">
         <v>22.6</v>
       </c>
-      <c r="L79">
+      <c r="L79" s="1">
         <v>25.8</v>
       </c>
-      <c r="M79">
+      <c r="M79" s="1">
         <v>23.7</v>
       </c>
-      <c r="N79">
+      <c r="N79" s="1">
         <v>24.1</v>
       </c>
-      <c r="O79">
+      <c r="O79" s="1">
         <v>25.8</v>
       </c>
-      <c r="P79">
+      <c r="P79" s="1">
         <v>20.3</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="A80" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E80" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="E80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="1">
         <v>10.4</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="1">
         <v>11.5</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="1">
         <v>12</v>
       </c>
-      <c r="J80">
+      <c r="J80" s="1">
         <v>12.7</v>
       </c>
-      <c r="K80">
+      <c r="K80" s="1">
         <v>13</v>
       </c>
-      <c r="L80">
+      <c r="L80" s="1">
         <v>13</v>
       </c>
-      <c r="M80">
+      <c r="M80" s="1">
         <v>13.5</v>
       </c>
-      <c r="N80">
+      <c r="N80" s="1">
         <v>13.4</v>
       </c>
-      <c r="O80">
+      <c r="O80" s="1">
         <v>14.2</v>
       </c>
-      <c r="P80">
+      <c r="P80" s="1">
         <v>12.7</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="A82" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="E82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="1">
         <v>14</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="1">
         <v>15</v>
       </c>
-      <c r="I82">
-        <v>10</v>
-      </c>
-      <c r="J82">
+      <c r="I82" s="1">
+        <v>10</v>
+      </c>
+      <c r="J82" s="1">
         <v>14</v>
       </c>
-      <c r="K82">
-        <v>10</v>
-      </c>
-      <c r="L82">
+      <c r="K82" s="1">
+        <v>10</v>
+      </c>
+      <c r="L82" s="1">
         <v>19</v>
       </c>
-      <c r="M82">
+      <c r="M82" s="1">
         <v>12</v>
       </c>
-      <c r="N82">
+      <c r="N82" s="1">
         <v>16</v>
       </c>
-      <c r="O82">
+      <c r="O82" s="1">
         <v>29</v>
       </c>
-      <c r="P82">
+      <c r="P82" s="1">
         <v>139</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="A83" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E83" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="E83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="1">
         <v>56</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="1">
         <v>61</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="1">
         <v>61</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="1">
         <v>114</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="1">
         <v>154</v>
       </c>
-      <c r="L83">
+      <c r="L83" s="1">
         <v>206</v>
       </c>
-      <c r="M83">
+      <c r="M83" s="1">
         <v>199</v>
       </c>
-      <c r="N83">
+      <c r="N83" s="1">
         <v>168</v>
       </c>
-      <c r="O83">
+      <c r="O83" s="1">
         <v>213</v>
       </c>
-      <c r="P83">
+      <c r="P83" s="1">
         <v>1232</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E84" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="E84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="1">
         <v>25</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="1">
         <v>31</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="1">
         <v>43</v>
       </c>
-      <c r="J84">
+      <c r="J84" s="1">
         <v>38</v>
       </c>
-      <c r="K84">
+      <c r="K84" s="1">
         <v>52</v>
       </c>
-      <c r="L84">
+      <c r="L84" s="1">
         <v>60</v>
       </c>
-      <c r="M84">
+      <c r="M84" s="1">
         <v>44</v>
       </c>
-      <c r="N84">
+      <c r="N84" s="1">
         <v>42</v>
       </c>
-      <c r="O84">
+      <c r="O84" s="1">
         <v>61</v>
       </c>
-      <c r="P84">
+      <c r="P84" s="1">
         <v>396</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="A85" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="E85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="1">
         <v>143</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="1">
         <v>146</v>
       </c>
-      <c r="I85">
+      <c r="I85" s="1">
         <v>180</v>
       </c>
-      <c r="J85">
+      <c r="J85" s="1">
         <v>211</v>
       </c>
-      <c r="K85">
+      <c r="K85" s="1">
         <v>222</v>
       </c>
-      <c r="L85">
+      <c r="L85" s="1">
         <v>251</v>
       </c>
-      <c r="M85">
+      <c r="M85" s="1">
         <v>275</v>
       </c>
-      <c r="N85">
+      <c r="N85" s="1">
         <v>303</v>
       </c>
-      <c r="O85">
+      <c r="O85" s="1">
         <v>403</v>
       </c>
-      <c r="P85">
+      <c r="P85" s="1">
         <v>2134</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="A86" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E86" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="E86" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="1">
         <v>162</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="1">
         <v>185</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="1">
         <v>239</v>
       </c>
-      <c r="J86">
+      <c r="J86" s="1">
         <v>273</v>
       </c>
-      <c r="K86">
+      <c r="K86" s="1">
         <v>329</v>
       </c>
-      <c r="L86">
+      <c r="L86" s="1">
         <v>321</v>
       </c>
-      <c r="M86">
+      <c r="M86" s="1">
         <v>353</v>
       </c>
-      <c r="N86">
+      <c r="N86" s="1">
         <v>356</v>
       </c>
-      <c r="O86">
+      <c r="O86" s="1">
         <v>393</v>
       </c>
-      <c r="P86">
+      <c r="P86" s="1">
         <v>2611</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="A87" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E87" t="s">
-        <v>11</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="E87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="1">
         <v>23</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="1">
         <v>43</v>
       </c>
-      <c r="I87">
+      <c r="I87" s="1">
         <v>58</v>
       </c>
-      <c r="J87">
+      <c r="J87" s="1">
         <v>115</v>
       </c>
-      <c r="K87">
+      <c r="K87" s="1">
         <v>213</v>
       </c>
-      <c r="L87">
+      <c r="L87" s="1">
         <v>264</v>
       </c>
-      <c r="M87">
+      <c r="M87" s="1">
         <v>220</v>
       </c>
-      <c r="N87">
+      <c r="N87" s="1">
         <v>211</v>
       </c>
-      <c r="O87">
+      <c r="O87" s="1">
         <v>262</v>
       </c>
-      <c r="P87">
+      <c r="P87" s="1">
         <v>1409</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="A88" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E88" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" t="s">
+      <c r="E88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="1">
         <v>4000</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="1">
         <v>4354</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="1">
         <v>4722</v>
       </c>
-      <c r="J88">
+      <c r="J88" s="1">
         <v>5364</v>
       </c>
-      <c r="K88">
+      <c r="K88" s="1">
         <v>6030</v>
       </c>
-      <c r="L88">
+      <c r="L88" s="1">
         <v>6286</v>
       </c>
-      <c r="M88">
+      <c r="M88" s="1">
         <v>6103</v>
       </c>
-      <c r="N88">
+      <c r="N88" s="1">
         <v>6170</v>
       </c>
-      <c r="O88">
+      <c r="O88" s="1">
         <v>7073</v>
       </c>
-      <c r="P88">
+      <c r="P88" s="1">
         <v>50102</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="A89" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="A90" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D90" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" t="s">
+      <c r="D90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="1">
         <v>19.3</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="1">
         <v>11.5</v>
       </c>
-      <c r="I90">
+      <c r="I90" s="1">
         <v>14.5</v>
       </c>
-      <c r="J90">
+      <c r="J90" s="1">
         <v>15.4</v>
       </c>
-      <c r="K90">
+      <c r="K90" s="1">
         <v>15.5</v>
       </c>
-      <c r="L90">
+      <c r="L90" s="1">
         <v>18</v>
       </c>
-      <c r="M90">
+      <c r="M90" s="1">
         <v>16.899999999999999</v>
       </c>
-      <c r="N90">
+      <c r="N90" s="1">
         <v>19.399999999999999</v>
       </c>
-      <c r="O90">
+      <c r="O90" s="1">
         <v>20.6</v>
       </c>
-      <c r="P90">
+      <c r="P90" s="1">
         <v>17.100000000000001</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="A91" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D91" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="D91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="1">
         <v>23.9</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="1">
         <v>21.8</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="1">
         <v>23</v>
       </c>
-      <c r="J91">
+      <c r="J91" s="1">
         <v>25.8</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="1">
         <v>26.2</v>
       </c>
-      <c r="L91">
+      <c r="L91" s="1">
         <v>27.5</v>
       </c>
-      <c r="M91">
+      <c r="M91" s="1">
         <v>32.5</v>
       </c>
-      <c r="N91">
+      <c r="N91" s="1">
         <v>36.4</v>
       </c>
-      <c r="O91">
+      <c r="O91" s="1">
         <v>36.6</v>
       </c>
-      <c r="P91">
+      <c r="P91" s="1">
         <v>29.3</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="A92" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D92" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="D92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="1">
         <v>23.9</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="1">
         <v>22</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="1">
         <v>20.100000000000001</v>
       </c>
-      <c r="J92">
+      <c r="J92" s="1">
         <v>23.7</v>
       </c>
-      <c r="K92">
+      <c r="K92" s="1">
         <v>20.100000000000001</v>
       </c>
-      <c r="L92">
+      <c r="L92" s="1">
         <v>19.399999999999999</v>
       </c>
-      <c r="M92">
+      <c r="M92" s="1">
         <v>28.4</v>
       </c>
-      <c r="N92">
+      <c r="N92" s="1">
         <v>27.4</v>
       </c>
-      <c r="O92">
+      <c r="O92" s="1">
         <v>29.3</v>
       </c>
-      <c r="P92">
+      <c r="P92" s="1">
         <v>24.2</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="A93" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D93" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" t="s">
-        <v>11</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="D93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="1">
         <v>32</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="1">
         <v>31.6</v>
       </c>
-      <c r="I93">
+      <c r="I93" s="1">
         <v>32.200000000000003</v>
       </c>
-      <c r="J93">
+      <c r="J93" s="1">
         <v>35.200000000000003</v>
       </c>
-      <c r="K93">
+      <c r="K93" s="1">
         <v>31.2</v>
       </c>
-      <c r="L93">
+      <c r="L93" s="1">
         <v>32.799999999999997</v>
       </c>
-      <c r="M93">
+      <c r="M93" s="1">
         <v>33.200000000000003</v>
       </c>
-      <c r="N93">
+      <c r="N93" s="1">
         <v>38</v>
       </c>
-      <c r="O93">
+      <c r="O93" s="1">
         <v>43</v>
       </c>
-      <c r="P93">
+      <c r="P93" s="1">
         <v>34.799999999999997</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="A94" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D94" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="D94" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G94">
+      <c r="G94" s="1">
         <v>37.9</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="1">
         <v>37</v>
       </c>
-      <c r="I94">
+      <c r="I94" s="1">
         <v>38.4</v>
       </c>
-      <c r="J94">
+      <c r="J94" s="1">
         <v>37.799999999999997</v>
       </c>
-      <c r="K94">
+      <c r="K94" s="1">
         <v>41.6</v>
       </c>
-      <c r="L94">
+      <c r="L94" s="1">
         <v>40.1</v>
       </c>
-      <c r="M94">
+      <c r="M94" s="1">
         <v>44.1</v>
       </c>
-      <c r="N94">
+      <c r="N94" s="1">
         <v>43.9</v>
       </c>
-      <c r="O94">
+      <c r="O94" s="1">
         <v>43.8</v>
       </c>
-      <c r="P94">
+      <c r="P94" s="1">
         <v>40.9</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="A95" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D95" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" t="s">
+      <c r="D95" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="1">
         <v>19.899999999999999</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="1">
         <v>21.9</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="1">
         <v>25.4</v>
       </c>
-      <c r="J95">
+      <c r="J95" s="1">
         <v>26.4</v>
       </c>
-      <c r="K95">
+      <c r="K95" s="1">
         <v>33.799999999999997</v>
       </c>
-      <c r="L95">
+      <c r="L95" s="1">
         <v>35.4</v>
       </c>
-      <c r="M95">
+      <c r="M95" s="1">
         <v>37.5</v>
       </c>
-      <c r="N95">
+      <c r="N95" s="1">
         <v>38.6</v>
       </c>
-      <c r="O95">
+      <c r="O95" s="1">
         <v>39.299999999999997</v>
       </c>
-      <c r="P95">
+      <c r="P95" s="1">
         <v>33.299999999999997</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="A96" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D96" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="D96" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="1">
         <v>33.9</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="1">
         <v>30.6</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="1">
         <v>29.1</v>
       </c>
-      <c r="J96">
+      <c r="J96" s="1">
         <v>30.2</v>
       </c>
-      <c r="K96">
+      <c r="K96" s="1">
         <v>30.8</v>
       </c>
-      <c r="L96">
+      <c r="L96" s="1">
         <v>28.5</v>
       </c>
-      <c r="M96">
+      <c r="M96" s="1">
         <v>33</v>
       </c>
-      <c r="N96">
+      <c r="N96" s="1">
         <v>33.299999999999997</v>
       </c>
-      <c r="O96">
+      <c r="O96" s="1">
         <v>33.9</v>
       </c>
-      <c r="P96">
+      <c r="P96" s="1">
         <v>31.5</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="A97" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="A98" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D98" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="D98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G98">
+      <c r="G98" s="1">
         <v>35</v>
       </c>
-      <c r="H98">
+      <c r="H98" s="1">
         <v>22</v>
       </c>
-      <c r="I98">
+      <c r="I98" s="1">
         <v>25</v>
       </c>
-      <c r="J98">
+      <c r="J98" s="1">
         <v>31</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="1">
         <v>30</v>
       </c>
-      <c r="L98">
+      <c r="L98" s="1">
         <v>39</v>
       </c>
-      <c r="M98">
+      <c r="M98" s="1">
         <v>37</v>
       </c>
-      <c r="N98">
+      <c r="N98" s="1">
         <v>44</v>
       </c>
-      <c r="O98">
+      <c r="O98" s="1">
         <v>64</v>
       </c>
-      <c r="P98">
+      <c r="P98" s="1">
         <v>327</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="A99" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D99" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="D99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G99">
+      <c r="G99" s="1">
         <v>142</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="1">
         <v>120</v>
       </c>
-      <c r="I99">
+      <c r="I99" s="1">
         <v>140</v>
       </c>
-      <c r="J99">
+      <c r="J99" s="1">
         <v>193</v>
       </c>
-      <c r="K99">
+      <c r="K99" s="1">
         <v>227</v>
       </c>
-      <c r="L99">
+      <c r="L99" s="1">
         <v>287</v>
       </c>
-      <c r="M99">
+      <c r="M99" s="1">
         <v>310</v>
       </c>
-      <c r="N99">
+      <c r="N99" s="1">
         <v>360</v>
       </c>
-      <c r="O99">
+      <c r="O99" s="1">
         <v>427</v>
       </c>
-      <c r="P99">
+      <c r="P99" s="1">
         <v>2206</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="A100" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D100" t="s">
-        <v>10</v>
-      </c>
-      <c r="E100" t="s">
-        <v>11</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="D100" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G100">
+      <c r="G100" s="1">
         <v>57</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="1">
         <v>51</v>
       </c>
-      <c r="I100">
+      <c r="I100" s="1">
         <v>61</v>
       </c>
-      <c r="J100">
+      <c r="J100" s="1">
         <v>77</v>
       </c>
-      <c r="K100">
+      <c r="K100" s="1">
         <v>90</v>
       </c>
-      <c r="L100">
+      <c r="L100" s="1">
         <v>95</v>
       </c>
-      <c r="M100">
+      <c r="M100" s="1">
         <v>127</v>
       </c>
-      <c r="N100">
+      <c r="N100" s="1">
         <v>127</v>
       </c>
-      <c r="O100">
+      <c r="O100" s="1">
         <v>153</v>
       </c>
-      <c r="P100">
+      <c r="P100" s="1">
         <v>838</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="A101" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D101" t="s">
-        <v>10</v>
-      </c>
-      <c r="E101" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="D101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G101">
+      <c r="G101" s="1">
         <v>262</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="1">
         <v>279</v>
       </c>
-      <c r="I101">
+      <c r="I101" s="1">
         <v>317</v>
       </c>
-      <c r="J101">
+      <c r="J101" s="1">
         <v>408</v>
       </c>
-      <c r="K101">
+      <c r="K101" s="1">
         <v>387</v>
       </c>
-      <c r="L101">
+      <c r="L101" s="1">
         <v>444</v>
       </c>
-      <c r="M101">
+      <c r="M101" s="1">
         <v>394</v>
       </c>
-      <c r="N101">
+      <c r="N101" s="1">
         <v>493</v>
       </c>
-      <c r="O101">
+      <c r="O101" s="1">
         <v>654</v>
       </c>
-      <c r="P101">
+      <c r="P101" s="1">
         <v>3638</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="A102" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D102" t="s">
-        <v>10</v>
-      </c>
-      <c r="E102" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="D102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G102">
+      <c r="G102" s="1">
         <v>384</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="1">
         <v>371</v>
       </c>
-      <c r="I102">
+      <c r="I102" s="1">
         <v>432</v>
       </c>
-      <c r="J102">
+      <c r="J102" s="1">
         <v>501</v>
       </c>
-      <c r="K102">
+      <c r="K102" s="1">
         <v>615</v>
       </c>
-      <c r="L102">
+      <c r="L102" s="1">
         <v>588</v>
       </c>
-      <c r="M102">
+      <c r="M102" s="1">
         <v>612</v>
       </c>
-      <c r="N102">
+      <c r="N102" s="1">
         <v>637</v>
       </c>
-      <c r="O102">
+      <c r="O102" s="1">
         <v>740</v>
       </c>
-      <c r="P102">
+      <c r="P102" s="1">
         <v>4880</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="A103" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D103" t="s">
-        <v>10</v>
-      </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="D103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G103">
+      <c r="G103" s="1">
         <v>57</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="1">
         <v>79</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="1">
         <v>117</v>
       </c>
-      <c r="J103">
+      <c r="J103" s="1">
         <v>148</v>
       </c>
-      <c r="K103">
+      <c r="K103" s="1">
         <v>275</v>
       </c>
-      <c r="L103">
+      <c r="L103" s="1">
         <v>333</v>
       </c>
-      <c r="M103">
+      <c r="M103" s="1">
         <v>314</v>
       </c>
-      <c r="N103">
+      <c r="N103" s="1">
         <v>299</v>
       </c>
-      <c r="O103">
+      <c r="O103" s="1">
         <v>359</v>
       </c>
-      <c r="P103">
+      <c r="P103" s="1">
         <v>1981</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="A104" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D104" t="s">
-        <v>10</v>
-      </c>
-      <c r="E104" t="s">
-        <v>11</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="D104" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G104">
+      <c r="G104" s="1">
         <v>10354</v>
       </c>
-      <c r="H104">
+      <c r="H104" s="1">
         <v>9360</v>
       </c>
-      <c r="I104">
+      <c r="I104" s="1">
         <v>9506</v>
       </c>
-      <c r="J104">
+      <c r="J104" s="1">
         <v>11123</v>
       </c>
-      <c r="K104">
+      <c r="K104" s="1">
         <v>12747</v>
       </c>
-      <c r="L104">
+      <c r="L104" s="1">
         <v>12331</v>
       </c>
-      <c r="M104">
+      <c r="M104" s="1">
         <v>12986</v>
       </c>
-      <c r="N104">
+      <c r="N104" s="1">
         <v>13696</v>
       </c>
-      <c r="O104">
+      <c r="O104" s="1">
         <v>15260</v>
       </c>
-      <c r="P104">
+      <c r="P104" s="1">
         <v>107363</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="A105" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="A106" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="A107" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="A108" s="1" t="s">
         <v>33</v>
       </c>
     </row>
